--- a/data/信用债发行汇总_2026-08-13.xlsx
+++ b/data/信用债发行汇总_2026-08-13.xlsx
@@ -1001,7 +1001,9 @@
           <t>2.10 ~ 2.75</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr"/>
+      <c r="H2" s="3" t="n">
+        <v>2.68</v>
+      </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
           <t>金融街控股股份有限公司</t>
@@ -1185,7 +1187,9 @@
           <t>2.00 ~ 2.65</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr"/>
+      <c r="H3" s="3" t="n">
+        <v>2.63</v>
+      </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
           <t>金融街控股股份有限公司</t>
